--- a/e_commerce_forms/008_festival_registration_form_with_eway--e_commerce_forms.xlsx
+++ b/e_commerce_forms/008_festival_registration_form_with_eway--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>festival_name</t>
+          <t>Festival Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>attendee_details</t>
+          <t>Attendee Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>Select One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>Select Multiple</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'option_1', 'value': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'option_2',_'value':_'option_prophets'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'option_2', 'value': 'option_prophets'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'option_three',_'value':_'option_three'}</t>
+          <t>option_three</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'option_three', 'value': 'option_three'}</t>
+          <t>option three</t>
         </is>
       </c>
     </row>
@@ -1216,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'option_1', 'value': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'option_2',_'value':_'option_two'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'option_2', 'value': 'option_two'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1250,97 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'option_three',_'value':_'option_three'}</t>
+          <t>option_three</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'option_three', 'value': 'option_three'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_18,_'label':_'option_1',_'value':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 18, 'label': 'option_1', 'value': 'option_1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_19,_'label':_'option_2',_'value':_'option_two'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 19, 'label': 'option_2', 'value': 'option_two'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_20,_'label':_'option_three',_'value':_'option_three'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 20, 'label': 'option_three', 'value': 'option_three'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>option three</t>
         </is>
       </c>
     </row>
